--- a/templates/daily_supply_plan.xlsx
+++ b/templates/daily_supply_plan.xlsx
@@ -137,67 +137,67 @@
   <dimension ref="A1:J502"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="19.0" customWidth="true"/>
+    <col min="1" max="1" width="18.0" customWidth="true"/>
     <col min="2" max="2" width="23.0" customWidth="true"/>
     <col min="3" max="3" width="31.0" customWidth="true"/>
     <col min="4" max="4" width="168.0" customWidth="true"/>
-    <col min="5" max="5" width="13.0" customWidth="true"/>
-    <col min="6" max="6" width="16.0" customWidth="true"/>
+    <col min="5" max="5" width="11.0" customWidth="true"/>
+    <col min="6" max="6" width="17.0" customWidth="true"/>
     <col min="7" max="7" width="16.0" customWidth="true"/>
-    <col min="8" max="8" width="23.0" customWidth="true"/>
-    <col min="9" max="9" width="23.0" customWidth="true"/>
-    <col min="10" max="10" width="23.0" customWidth="true"/>
+    <col min="8" max="8" width="17.0" customWidth="true"/>
+    <col min="9" max="9" width="17.0" customWidth="true"/>
+    <col min="10" max="10" width="17.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Customer Model</t>
+          <t>客户型号</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Product Model</t>
+          <t>产品型号</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>In-transit Warehouse(Code)</t>
+          <t>在途仓（编码）</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>Product Long Description</t>
+          <t>产品长描述</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>品类</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>Supply Date</t>
+          <t>供应日期</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>Supply Week</t>
+          <t>供应周</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>Scheduled Quantity</t>
+          <t>计划数量</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
-          <t>Allocated Quantity</t>
+          <t>占用数量</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>Available Quantity</t>
+          <t>可用数量</t>
         </is>
       </c>
     </row>
@@ -4553,10 +4553,10 @@
         <v>2592.0</v>
       </c>
       <c r="I98" s="12" t="n">
-        <v>6048.0</v>
+        <v>864.0</v>
       </c>
       <c r="J98" s="12" t="n">
-        <v>-3456.0</v>
+        <v>1728.0</v>
       </c>
     </row>
     <row r="99">
@@ -4872,13 +4872,13 @@
         </is>
       </c>
       <c r="H105" s="12" t="n">
-        <v>149.0</v>
+        <v>0.0</v>
       </c>
       <c r="I105" s="12" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="J105" s="12" t="n">
-        <v>144.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="106">
@@ -4918,13 +4918,13 @@
         </is>
       </c>
       <c r="H106" s="12" t="n">
-        <v>55.0</v>
+        <v>0.0</v>
       </c>
       <c r="I106" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J106" s="12" t="n">
-        <v>55.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="107">
@@ -4964,13 +4964,13 @@
         </is>
       </c>
       <c r="H107" s="12" t="n">
-        <v>316.0</v>
+        <v>0.0</v>
       </c>
       <c r="I107" s="12" t="n">
-        <v>229.0</v>
+        <v>0.0</v>
       </c>
       <c r="J107" s="12" t="n">
-        <v>87.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="108">
@@ -5010,13 +5010,13 @@
         </is>
       </c>
       <c r="H108" s="12" t="n">
-        <v>180.0</v>
+        <v>0.0</v>
       </c>
       <c r="I108" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J108" s="12" t="n">
-        <v>180.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="109">
@@ -5056,13 +5056,13 @@
         </is>
       </c>
       <c r="H109" s="12" t="n">
-        <v>520.0</v>
+        <v>0.0</v>
       </c>
       <c r="I109" s="12" t="n">
-        <v>203.0</v>
+        <v>0.0</v>
       </c>
       <c r="J109" s="12" t="n">
-        <v>317.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="110">
@@ -6157,10 +6157,10 @@
         <v>2376.0</v>
       </c>
       <c r="I134" s="12" t="n">
-        <v>2376.0</v>
+        <v>1080.0</v>
       </c>
       <c r="J134" s="12" t="n">
-        <v>0.0</v>
+        <v>1296.0</v>
       </c>
     </row>
     <row r="135">
@@ -6598,13 +6598,13 @@
         </is>
       </c>
       <c r="H144" s="12" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I144" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J144" s="12" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="145">
@@ -6640,13 +6640,13 @@
         </is>
       </c>
       <c r="H145" s="12" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="I145" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J145" s="12" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="146">
@@ -6682,13 +6682,13 @@
         </is>
       </c>
       <c r="H146" s="12" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I146" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J146" s="12" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="147">
@@ -6724,13 +6724,13 @@
         </is>
       </c>
       <c r="H147" s="12" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="I147" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J147" s="12" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="148">
@@ -6980,13 +6980,13 @@
         </is>
       </c>
       <c r="H153" s="12" t="n">
-        <v>3744.0</v>
+        <v>1872.0</v>
       </c>
       <c r="I153" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J153" s="12" t="n">
-        <v>3744.0</v>
+        <v>1872.0</v>
       </c>
     </row>
     <row r="154">
@@ -7026,13 +7026,13 @@
         </is>
       </c>
       <c r="H154" s="12" t="n">
-        <v>7776.0</v>
+        <v>5184.0</v>
       </c>
       <c r="I154" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J154" s="12" t="n">
-        <v>7776.0</v>
+        <v>5184.0</v>
       </c>
     </row>
     <row r="155">
@@ -7118,10 +7118,10 @@
         </is>
       </c>
       <c r="H156" s="12" t="n">
-        <v>8640.0</v>
+        <v>5184.0</v>
       </c>
       <c r="I156" s="12" t="n">
-        <v>8640.0</v>
+        <v>5184.0</v>
       </c>
       <c r="J156" s="12" t="n">
         <v>0.0</v>
@@ -7167,10 +7167,10 @@
         <v>0.0</v>
       </c>
       <c r="I157" s="12" t="n">
-        <v>1440.0</v>
+        <v>0.0</v>
       </c>
       <c r="J157" s="12" t="n">
-        <v>-1440.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="158">
@@ -7213,10 +7213,10 @@
         <v>350.0</v>
       </c>
       <c r="I158" s="12" t="n">
-        <v>25.0</v>
+        <v>61.0</v>
       </c>
       <c r="J158" s="12" t="n">
-        <v>325.0</v>
+        <v>289.0</v>
       </c>
     </row>
     <row r="159">
@@ -7803,10 +7803,10 @@
         <v>4752.0</v>
       </c>
       <c r="I171" s="12" t="n">
-        <v>3276.0</v>
+        <v>2664.0</v>
       </c>
       <c r="J171" s="12" t="n">
-        <v>1476.0</v>
+        <v>2088.0</v>
       </c>
     </row>
     <row r="172">
@@ -8541,10 +8541,10 @@
         <v>7776.0</v>
       </c>
       <c r="I188" s="12" t="n">
-        <v>6912.0</v>
+        <v>7776.0</v>
       </c>
       <c r="J188" s="12" t="n">
-        <v>864.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="189">
@@ -9099,10 +9099,10 @@
         <v>552.0</v>
       </c>
       <c r="I201" s="12" t="n">
-        <v>32.0</v>
+        <v>119.0</v>
       </c>
       <c r="J201" s="12" t="n">
-        <v>520.0</v>
+        <v>433.0</v>
       </c>
     </row>
     <row r="202">
@@ -10891,10 +10891,10 @@
         <v>224.0</v>
       </c>
       <c r="I241" s="12" t="n">
-        <v>25.0</v>
+        <v>61.0</v>
       </c>
       <c r="J241" s="12" t="n">
-        <v>199.0</v>
+        <v>163.0</v>
       </c>
     </row>
     <row r="242">
@@ -12453,10 +12453,10 @@
         <v>426.0</v>
       </c>
       <c r="I276" s="12" t="n">
-        <v>275.0</v>
+        <v>271.0</v>
       </c>
       <c r="J276" s="12" t="n">
-        <v>151.0</v>
+        <v>155.0</v>
       </c>
     </row>
     <row r="277">
@@ -12545,10 +12545,10 @@
         <v>300.0</v>
       </c>
       <c r="I278" s="12" t="n">
-        <v>251.0</v>
+        <v>247.0</v>
       </c>
       <c r="J278" s="12" t="n">
-        <v>49.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="279">
@@ -12591,10 +12591,10 @@
         <v>552.0</v>
       </c>
       <c r="I279" s="12" t="n">
-        <v>256.0</v>
+        <v>248.0</v>
       </c>
       <c r="J279" s="12" t="n">
-        <v>296.0</v>
+        <v>304.0</v>
       </c>
     </row>
     <row r="280">
@@ -14246,13 +14246,13 @@
         </is>
       </c>
       <c r="H316" s="12" t="n">
-        <v>3168.0</v>
+        <v>2376.0</v>
       </c>
       <c r="I316" s="12" t="n">
-        <v>2160.0</v>
+        <v>2124.0</v>
       </c>
       <c r="J316" s="12" t="n">
-        <v>1008.0</v>
+        <v>252.0</v>
       </c>
     </row>
     <row r="317">
@@ -14295,10 +14295,10 @@
         <v>3960.0</v>
       </c>
       <c r="I317" s="12" t="n">
-        <v>3528.0</v>
+        <v>3384.0</v>
       </c>
       <c r="J317" s="12" t="n">
-        <v>432.0</v>
+        <v>576.0</v>
       </c>
     </row>
     <row r="318">
@@ -14697,10 +14697,10 @@
         <v>3456.0</v>
       </c>
       <c r="I326" s="12" t="n">
-        <v>864.0</v>
+        <v>1728.0</v>
       </c>
       <c r="J326" s="12" t="n">
-        <v>2592.0</v>
+        <v>1728.0</v>
       </c>
     </row>
     <row r="327">
@@ -14823,10 +14823,10 @@
         <v>1656.0</v>
       </c>
       <c r="I329" s="12" t="n">
-        <v>326.0</v>
+        <v>378.0</v>
       </c>
       <c r="J329" s="12" t="n">
-        <v>1330.0</v>
+        <v>1278.0</v>
       </c>
     </row>
     <row r="330">
@@ -15183,10 +15183,10 @@
         <v>7128.0</v>
       </c>
       <c r="I337" s="12" t="n">
-        <v>3528.0</v>
+        <v>6120.0</v>
       </c>
       <c r="J337" s="12" t="n">
-        <v>3600.0</v>
+        <v>1008.0</v>
       </c>
     </row>
     <row r="338">
@@ -15565,10 +15565,10 @@
         <v>4320.0</v>
       </c>
       <c r="I346" s="12" t="n">
-        <v>1440.0</v>
+        <v>4320.0</v>
       </c>
       <c r="J346" s="12" t="n">
-        <v>2880.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="347">
@@ -15607,10 +15607,10 @@
         <v>9360.0</v>
       </c>
       <c r="I347" s="12" t="n">
-        <v>6552.0</v>
+        <v>7488.0</v>
       </c>
       <c r="J347" s="12" t="n">
-        <v>2808.0</v>
+        <v>1872.0</v>
       </c>
     </row>
     <row r="348">
@@ -17695,10 +17695,10 @@
         <v>30.0</v>
       </c>
       <c r="I395" s="12" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="J395" s="12" t="n">
-        <v>20.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="396">
@@ -18521,10 +18521,10 @@
         <v>260.0</v>
       </c>
       <c r="I414" s="12" t="n">
-        <v>31.0</v>
+        <v>27.0</v>
       </c>
       <c r="J414" s="12" t="n">
-        <v>229.0</v>
+        <v>233.0</v>
       </c>
     </row>
     <row r="415">
@@ -18563,10 +18563,10 @@
         <v>157.0</v>
       </c>
       <c r="I415" s="12" t="n">
-        <v>31.0</v>
+        <v>27.0</v>
       </c>
       <c r="J415" s="12" t="n">
-        <v>126.0</v>
+        <v>130.0</v>
       </c>
     </row>
     <row r="416">
@@ -19611,10 +19611,10 @@
         <v>3960.0</v>
       </c>
       <c r="I439" s="12" t="n">
-        <v>864.0</v>
+        <v>1296.0</v>
       </c>
       <c r="J439" s="12" t="n">
-        <v>3096.0</v>
+        <v>2664.0</v>
       </c>
     </row>
     <row r="440">
@@ -21333,10 +21333,10 @@
         <v>864.0</v>
       </c>
       <c r="I478" s="12" t="n">
-        <v>0.0</v>
+        <v>864.0</v>
       </c>
       <c r="J478" s="12" t="n">
-        <v>864.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="479">
@@ -21501,10 +21501,10 @@
         <v>4752.0</v>
       </c>
       <c r="I482" s="12" t="n">
-        <v>0.0</v>
+        <v>4752.0</v>
       </c>
       <c r="J482" s="12" t="n">
-        <v>4752.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="483">
@@ -21715,10 +21715,10 @@
         <v>2160.0</v>
       </c>
       <c r="I487" s="12" t="n">
-        <v>1440.0</v>
+        <v>2160.0</v>
       </c>
       <c r="J487" s="12" t="n">
-        <v>720.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="488">
@@ -21975,10 +21975,10 @@
         <v>720.0</v>
       </c>
       <c r="I493" s="12" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="J493" s="12" t="n">
         <v>720.0</v>
-      </c>
-      <c r="J493" s="12" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="494">

--- a/templates/daily_supply_plan.xlsx
+++ b/templates/daily_supply_plan.xlsx
@@ -137,67 +137,67 @@
   <dimension ref="A1:J502"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="18.0" customWidth="true"/>
+    <col min="1" max="1" width="19.0" customWidth="true"/>
     <col min="2" max="2" width="23.0" customWidth="true"/>
     <col min="3" max="3" width="31.0" customWidth="true"/>
     <col min="4" max="4" width="168.0" customWidth="true"/>
-    <col min="5" max="5" width="11.0" customWidth="true"/>
+    <col min="5" max="5" width="13.0" customWidth="true"/>
     <col min="6" max="6" width="17.0" customWidth="true"/>
     <col min="7" max="7" width="16.0" customWidth="true"/>
-    <col min="8" max="8" width="17.0" customWidth="true"/>
-    <col min="9" max="9" width="17.0" customWidth="true"/>
-    <col min="10" max="10" width="17.0" customWidth="true"/>
+    <col min="8" max="8" width="23.0" customWidth="true"/>
+    <col min="9" max="9" width="23.0" customWidth="true"/>
+    <col min="10" max="10" width="23.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>客户型号</t>
+          <t>Customer Model</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>产品型号</t>
+          <t>Product Model</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>在途仓（编码）</t>
+          <t>In-transit Warehouse(Code)</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>产品长描述</t>
+          <t>Product Long Description</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>品类</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>供应日期</t>
+          <t>Supply Date</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>供应周</t>
+          <t>Supply Week</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>计划数量</t>
+          <t>Scheduled Quantity</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
-          <t>占用数量</t>
+          <t>Allocated Quantity</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>可用数量</t>
+          <t>Available Quantity</t>
         </is>
       </c>
     </row>
@@ -306,7 +306,7 @@
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPUK(PVLFR027)</t>
+          <t>Arrival Plan-SPTN(PVLFR024)</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
@@ -352,7 +352,7 @@
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPTN(PVLFR024)</t>
+          <t>Arrival Plan-SPUK(PVLFR027)</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
@@ -574,7 +574,7 @@
       <c r="B10" s="12"/>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPUK(PVLFR027)</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
@@ -616,7 +616,7 @@
       <c r="B11" s="12"/>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPUK(PVLFR027)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPUK(PVLFR027)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPUK(PVLFR027)</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPES(PVLFR026)</t>
+          <t>Arrival Plan-SPTN(PVLFR024)</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPUK(PVLFR027)</t>
+          <t>Arrival Plan-SPES(PVLFR026)</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPTN(PVLFR024)</t>
+          <t>Arrival Plan-SPUK(PVLFR027)</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPIT(PVLFR025)</t>
         </is>
       </c>
       <c r="D90" s="12" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPIT(PVLFR025)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPUK(PVLFR027)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D97" s="12" t="inlineStr">
@@ -4504,13 +4504,13 @@
         </is>
       </c>
       <c r="H97" s="12" t="n">
-        <v>0.0</v>
+        <v>2592.0</v>
       </c>
       <c r="I97" s="12" t="n">
-        <v>0.0</v>
+        <v>864.0</v>
       </c>
       <c r="J97" s="12" t="n">
-        <v>0.0</v>
+        <v>1728.0</v>
       </c>
     </row>
     <row r="98">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="C98" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPUK(PVLFR027)</t>
         </is>
       </c>
       <c r="D98" s="12" t="inlineStr">
@@ -4550,13 +4550,13 @@
         </is>
       </c>
       <c r="H98" s="12" t="n">
-        <v>2592.0</v>
+        <v>0.0</v>
       </c>
       <c r="I98" s="12" t="n">
-        <v>864.0</v>
+        <v>0.0</v>
       </c>
       <c r="J98" s="12" t="n">
-        <v>1728.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="99">
@@ -5292,7 +5292,7 @@
       <c r="B115" s="12"/>
       <c r="C115" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPTN(PVLFR024)</t>
         </is>
       </c>
       <c r="D115" s="12" t="inlineStr">
@@ -5334,7 +5334,7 @@
       <c r="B116" s="12"/>
       <c r="C116" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPTN(PVLFR024)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D116" s="12" t="inlineStr">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="C172" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPIT(PVLFR025)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D172" s="12" t="inlineStr">
@@ -7846,10 +7846,10 @@
         </is>
       </c>
       <c r="H172" s="12" t="n">
-        <v>0.0</v>
+        <v>1584.0</v>
       </c>
       <c r="I172" s="12" t="n">
-        <v>0.0</v>
+        <v>1584.0</v>
       </c>
       <c r="J172" s="12" t="n">
         <v>0.0</v>
@@ -7868,7 +7868,7 @@
       </c>
       <c r="C173" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPIT(PVLFR025)</t>
         </is>
       </c>
       <c r="D173" s="12" t="inlineStr">
@@ -7892,10 +7892,10 @@
         </is>
       </c>
       <c r="H173" s="12" t="n">
-        <v>1584.0</v>
+        <v>0.0</v>
       </c>
       <c r="I173" s="12" t="n">
-        <v>1584.0</v>
+        <v>0.0</v>
       </c>
       <c r="J173" s="12" t="n">
         <v>0.0</v>
@@ -8044,7 +8044,7 @@
       <c r="B177" s="12"/>
       <c r="C177" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPTN(PVLFR024)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D177" s="12" t="inlineStr">
@@ -8086,7 +8086,7 @@
       <c r="B178" s="12"/>
       <c r="C178" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPTN(PVLFR024)</t>
         </is>
       </c>
       <c r="D178" s="12" t="inlineStr">
@@ -8808,7 +8808,7 @@
       <c r="B195" s="12"/>
       <c r="C195" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPUK(PVLFR027)</t>
         </is>
       </c>
       <c r="D195" s="12" t="inlineStr">
@@ -8832,13 +8832,13 @@
         </is>
       </c>
       <c r="H195" s="12" t="n">
-        <v>0.0</v>
+        <v>1584.0</v>
       </c>
       <c r="I195" s="12" t="n">
-        <v>0.0</v>
+        <v>720.0</v>
       </c>
       <c r="J195" s="12" t="n">
-        <v>0.0</v>
+        <v>864.0</v>
       </c>
     </row>
     <row r="196">
@@ -8850,7 +8850,7 @@
       <c r="B196" s="12"/>
       <c r="C196" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPUK(PVLFR027)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D196" s="12" t="inlineStr">
@@ -8874,13 +8874,13 @@
         </is>
       </c>
       <c r="H196" s="12" t="n">
-        <v>1584.0</v>
+        <v>0.0</v>
       </c>
       <c r="I196" s="12" t="n">
-        <v>720.0</v>
+        <v>0.0</v>
       </c>
       <c r="J196" s="12" t="n">
-        <v>864.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="197">
@@ -10082,7 +10082,7 @@
       </c>
       <c r="C224" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPUK(PVLFR027)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D224" s="12" t="inlineStr">
@@ -10174,7 +10174,7 @@
       </c>
       <c r="C226" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPUK(PVLFR027)</t>
         </is>
       </c>
       <c r="D226" s="12" t="inlineStr">
@@ -10358,7 +10358,7 @@
       </c>
       <c r="C230" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPTN(PVLFR024)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D230" s="12" t="inlineStr">
@@ -10382,10 +10382,10 @@
         </is>
       </c>
       <c r="H230" s="12" t="n">
-        <v>7200.0</v>
+        <v>0.0</v>
       </c>
       <c r="I230" s="12" t="n">
-        <v>7200.0</v>
+        <v>0.0</v>
       </c>
       <c r="J230" s="12" t="n">
         <v>0.0</v>
@@ -10404,7 +10404,7 @@
       </c>
       <c r="C231" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPTN(PVLFR024)</t>
         </is>
       </c>
       <c r="D231" s="12" t="inlineStr">
@@ -10428,10 +10428,10 @@
         </is>
       </c>
       <c r="H231" s="12" t="n">
-        <v>0.0</v>
+        <v>7200.0</v>
       </c>
       <c r="I231" s="12" t="n">
-        <v>0.0</v>
+        <v>7200.0</v>
       </c>
       <c r="J231" s="12" t="n">
         <v>0.0</v>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="C234" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPTN(PVLFR024)</t>
         </is>
       </c>
       <c r="D234" s="12" t="inlineStr">
@@ -10588,7 +10588,7 @@
       </c>
       <c r="C235" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPTN(PVLFR024)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D235" s="12" t="inlineStr">
@@ -10956,7 +10956,7 @@
       </c>
       <c r="C243" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPUK(PVLFR027)</t>
+          <t>Arrival Plan-SPIT(PVLFR025)</t>
         </is>
       </c>
       <c r="D243" s="12" t="inlineStr">
@@ -11002,7 +11002,7 @@
       </c>
       <c r="C244" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPIT(PVLFR025)</t>
+          <t>Arrival Plan-SPES(PVLFR026)</t>
         </is>
       </c>
       <c r="D244" s="12" t="inlineStr">
@@ -11048,7 +11048,7 @@
       </c>
       <c r="C245" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPES(PVLFR026)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D245" s="12" t="inlineStr">
@@ -11094,7 +11094,7 @@
       </c>
       <c r="C246" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPUK(PVLFR027)</t>
         </is>
       </c>
       <c r="D246" s="12" t="inlineStr">
@@ -11232,7 +11232,7 @@
       </c>
       <c r="C249" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPTN(PVLFR024)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D249" s="12" t="inlineStr">
@@ -11256,13 +11256,13 @@
         </is>
       </c>
       <c r="H249" s="12" t="n">
-        <v>0.0</v>
+        <v>9504.0</v>
       </c>
       <c r="I249" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J249" s="12" t="n">
-        <v>0.0</v>
+        <v>9504.0</v>
       </c>
     </row>
     <row r="250">
@@ -11278,7 +11278,7 @@
       </c>
       <c r="C250" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPTN(PVLFR024)</t>
         </is>
       </c>
       <c r="D250" s="12" t="inlineStr">
@@ -11302,13 +11302,13 @@
         </is>
       </c>
       <c r="H250" s="12" t="n">
-        <v>9504.0</v>
+        <v>0.0</v>
       </c>
       <c r="I250" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J250" s="12" t="n">
-        <v>9504.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="251">
@@ -14314,7 +14314,7 @@
       </c>
       <c r="C318" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPIT(PVLFR025)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D318" s="12" t="inlineStr">
@@ -14360,7 +14360,7 @@
       </c>
       <c r="C319" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPIT(PVLFR025)</t>
         </is>
       </c>
       <c r="D319" s="12" t="inlineStr">
@@ -14972,7 +14972,7 @@
       </c>
       <c r="C333" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPUK(PVLFR027)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D333" s="12" t="inlineStr">
@@ -14996,10 +14996,10 @@
         </is>
       </c>
       <c r="H333" s="12" t="n">
-        <v>936.0</v>
+        <v>4680.0</v>
       </c>
       <c r="I333" s="12" t="n">
-        <v>936.0</v>
+        <v>4680.0</v>
       </c>
       <c r="J333" s="12" t="n">
         <v>0.0</v>
@@ -15018,7 +15018,7 @@
       </c>
       <c r="C334" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPUK(PVLFR027)</t>
         </is>
       </c>
       <c r="D334" s="12" t="inlineStr">
@@ -15042,10 +15042,10 @@
         </is>
       </c>
       <c r="H334" s="12" t="n">
-        <v>4680.0</v>
+        <v>936.0</v>
       </c>
       <c r="I334" s="12" t="n">
-        <v>4680.0</v>
+        <v>936.0</v>
       </c>
       <c r="J334" s="12" t="n">
         <v>0.0</v>
@@ -16196,7 +16196,7 @@
       </c>
       <c r="C361" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPTN(PVLFR024)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D361" s="12" t="inlineStr">
@@ -16220,13 +16220,13 @@
         </is>
       </c>
       <c r="H361" s="12" t="n">
-        <v>864.0</v>
+        <v>1728.0</v>
       </c>
       <c r="I361" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J361" s="12" t="n">
-        <v>864.0</v>
+        <v>1728.0</v>
       </c>
     </row>
     <row r="362">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="C362" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPTN(PVLFR024)</t>
         </is>
       </c>
       <c r="D362" s="12" t="inlineStr">
@@ -16266,13 +16266,13 @@
         </is>
       </c>
       <c r="H362" s="12" t="n">
-        <v>1728.0</v>
+        <v>864.0</v>
       </c>
       <c r="I362" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J362" s="12" t="n">
-        <v>1728.0</v>
+        <v>864.0</v>
       </c>
     </row>
     <row r="363">
@@ -16518,7 +16518,7 @@
       </c>
       <c r="C368" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPTN(PVLFR024)</t>
         </is>
       </c>
       <c r="D368" s="12" t="inlineStr">
@@ -16542,13 +16542,13 @@
         </is>
       </c>
       <c r="H368" s="12" t="n">
-        <v>3456.0</v>
+        <v>1728.0</v>
       </c>
       <c r="I368" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J368" s="12" t="n">
-        <v>3456.0</v>
+        <v>1728.0</v>
       </c>
     </row>
     <row r="369">
@@ -16564,7 +16564,7 @@
       </c>
       <c r="C369" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPTN(PVLFR024)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D369" s="12" t="inlineStr">
@@ -16588,13 +16588,13 @@
         </is>
       </c>
       <c r="H369" s="12" t="n">
-        <v>1728.0</v>
+        <v>3456.0</v>
       </c>
       <c r="I369" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J369" s="12" t="n">
-        <v>1728.0</v>
+        <v>3456.0</v>
       </c>
     </row>
     <row r="370">
@@ -16606,7 +16606,7 @@
       <c r="B370" s="12"/>
       <c r="C370" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPNL(PVLFR028)</t>
+          <t>Arrival Plan-SPTN(PVLFR024)</t>
         </is>
       </c>
       <c r="D370" s="12" t="inlineStr">
@@ -16630,13 +16630,13 @@
         </is>
       </c>
       <c r="H370" s="12" t="n">
-        <v>5184.0</v>
+        <v>4320.0</v>
       </c>
       <c r="I370" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J370" s="12" t="n">
-        <v>5184.0</v>
+        <v>4320.0</v>
       </c>
     </row>
     <row r="371">
@@ -16648,7 +16648,7 @@
       <c r="B371" s="12"/>
       <c r="C371" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPTN(PVLFR024)</t>
+          <t>Arrival Plan-SPNL(PVLFR028)</t>
         </is>
       </c>
       <c r="D371" s="12" t="inlineStr">
@@ -16672,13 +16672,13 @@
         </is>
       </c>
       <c r="H371" s="12" t="n">
-        <v>4320.0</v>
+        <v>5184.0</v>
       </c>
       <c r="I371" s="12" t="n">
         <v>0.0</v>
       </c>
       <c r="J371" s="12" t="n">
-        <v>4320.0</v>
+        <v>5184.0</v>
       </c>
     </row>
     <row r="372">
@@ -18968,7 +18968,7 @@
       </c>
       <c r="C425" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPUK(PVLFR027)</t>
+          <t>Arrival Plan-SPTN(PVLFR024)</t>
         </is>
       </c>
       <c r="D425" s="12" t="inlineStr">
@@ -19060,7 +19060,7 @@
       </c>
       <c r="C427" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPTN(PVLFR024)</t>
+          <t>Arrival Plan-SPUK(PVLFR027)</t>
         </is>
       </c>
       <c r="D427" s="12" t="inlineStr">
@@ -19584,7 +19584,7 @@
       <c r="B439" s="12"/>
       <c r="C439" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPIT(PVLFR025)</t>
+          <t>Arrival Plan-SPES(PVLFR026)</t>
         </is>
       </c>
       <c r="D439" s="12" t="inlineStr">
@@ -19608,13 +19608,13 @@
         </is>
       </c>
       <c r="H439" s="12" t="n">
-        <v>3960.0</v>
+        <v>792.0</v>
       </c>
       <c r="I439" s="12" t="n">
-        <v>1296.0</v>
+        <v>0.0</v>
       </c>
       <c r="J439" s="12" t="n">
-        <v>2664.0</v>
+        <v>792.0</v>
       </c>
     </row>
     <row r="440">
@@ -19626,7 +19626,7 @@
       <c r="B440" s="12"/>
       <c r="C440" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPES(PVLFR026)</t>
+          <t>Arrival Plan-SPIT(PVLFR025)</t>
         </is>
       </c>
       <c r="D440" s="12" t="inlineStr">
@@ -19650,13 +19650,13 @@
         </is>
       </c>
       <c r="H440" s="12" t="n">
-        <v>792.0</v>
+        <v>3960.0</v>
       </c>
       <c r="I440" s="12" t="n">
-        <v>0.0</v>
+        <v>1296.0</v>
       </c>
       <c r="J440" s="12" t="n">
-        <v>792.0</v>
+        <v>2664.0</v>
       </c>
     </row>
     <row r="441">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="C462" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPUK(PVLFR027)</t>
+          <t>Arrival Plan-SPTN(PVLFR024)</t>
         </is>
       </c>
       <c r="D462" s="12" t="inlineStr">
@@ -20640,7 +20640,7 @@
       </c>
       <c r="C463" s="12" t="inlineStr">
         <is>
-          <t>Arrival Plan-SPTN(PVLFR024)</t>
+          <t>Arrival Plan-SPUK(PVLFR027)</t>
         </is>
       </c>
       <c r="D463" s="12" t="inlineStr">

--- a/templates/daily_supply_plan.xlsx
+++ b/templates/daily_supply_plan.xlsx
@@ -6246,13 +6246,13 @@
         </is>
       </c>
       <c r="H136" s="12" t="n">
-        <v>5544.0</v>
+        <v>2376.0</v>
       </c>
       <c r="I136" s="12" t="n">
         <v>3456.0</v>
       </c>
       <c r="J136" s="12" t="n">
-        <v>2088.0</v>
+        <v>-1080.0</v>
       </c>
     </row>
     <row r="137">
@@ -7478,10 +7478,10 @@
         </is>
       </c>
       <c r="H164" s="12" t="n">
-        <v>3960.0</v>
+        <v>3168.0</v>
       </c>
       <c r="I164" s="12" t="n">
-        <v>3960.0</v>
+        <v>3168.0</v>
       </c>
       <c r="J164" s="12" t="n">
         <v>0.0</v>
@@ -8944,10 +8944,10 @@
         </is>
       </c>
       <c r="H197" s="12" t="n">
-        <v>7776.0</v>
+        <v>6912.0</v>
       </c>
       <c r="I197" s="12" t="n">
-        <v>7776.0</v>
+        <v>6912.0</v>
       </c>
       <c r="J197" s="12" t="n">
         <v>0.0</v>
@@ -13189,10 +13189,10 @@
         <v>7128.0</v>
       </c>
       <c r="I292" s="12" t="n">
-        <v>5472.0</v>
+        <v>6336.0</v>
       </c>
       <c r="J292" s="12" t="n">
-        <v>1656.0</v>
+        <v>792.0</v>
       </c>
     </row>
     <row r="293">
@@ -15253,10 +15253,10 @@
         <v>2376.0</v>
       </c>
       <c r="I338" s="12" t="n">
-        <v>2376.0</v>
+        <v>2196.0</v>
       </c>
       <c r="J338" s="12" t="n">
-        <v>0.0</v>
+        <v>180.0</v>
       </c>
     </row>
     <row r="339">
@@ -16081,10 +16081,10 @@
         <v>1584.0</v>
       </c>
       <c r="I356" s="12" t="n">
-        <v>828.0</v>
+        <v>1008.0</v>
       </c>
       <c r="J356" s="12" t="n">
-        <v>756.0</v>
+        <v>576.0</v>
       </c>
     </row>
     <row r="357">
@@ -19487,10 +19487,10 @@
         <v>1584.0</v>
       </c>
       <c r="I433" s="12" t="n">
-        <v>792.0</v>
+        <v>1152.0</v>
       </c>
       <c r="J433" s="12" t="n">
-        <v>792.0</v>
+        <v>432.0</v>
       </c>
     </row>
     <row r="434">
@@ -20845,10 +20845,10 @@
         <v>1584.0</v>
       </c>
       <c r="I464" s="12" t="n">
-        <v>864.0</v>
+        <v>1584.0</v>
       </c>
       <c r="J464" s="12" t="n">
-        <v>720.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="465">
@@ -21101,10 +21101,10 @@
         <v>4680.0</v>
       </c>
       <c r="I470" s="12" t="n">
-        <v>936.0</v>
+        <v>2808.0</v>
       </c>
       <c r="J470" s="12" t="n">
-        <v>3744.0</v>
+        <v>1872.0</v>
       </c>
     </row>
     <row r="471">
@@ -22283,10 +22283,10 @@
         <v>720.0</v>
       </c>
       <c r="I497" s="12" t="n">
-        <v>0.0</v>
+        <v>720.0</v>
       </c>
       <c r="J497" s="12" t="n">
-        <v>720.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="498">
@@ -22619,10 +22619,10 @@
         <v>1584.0</v>
       </c>
       <c r="I505" s="12" t="n">
-        <v>936.0</v>
+        <v>1584.0</v>
       </c>
       <c r="J505" s="12" t="n">
-        <v>648.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="506">

--- a/templates/daily_supply_plan.xlsx
+++ b/templates/daily_supply_plan.xlsx
@@ -142,7 +142,7 @@
     <col min="3" max="3" width="31.0" customWidth="true"/>
     <col min="4" max="4" width="168.0" customWidth="true"/>
     <col min="5" max="5" width="13.0" customWidth="true"/>
-    <col min="6" max="6" width="16.0" customWidth="true"/>
+    <col min="6" max="6" width="17.0" customWidth="true"/>
     <col min="7" max="7" width="16.0" customWidth="true"/>
     <col min="8" max="8" width="23.0" customWidth="true"/>
     <col min="9" max="9" width="23.0" customWidth="true"/>
@@ -6249,10 +6249,10 @@
         <v>2376.0</v>
       </c>
       <c r="I136" s="12" t="n">
-        <v>3456.0</v>
+        <v>1872.0</v>
       </c>
       <c r="J136" s="12" t="n">
-        <v>-1080.0</v>
+        <v>504.0</v>
       </c>
     </row>
     <row r="137">
@@ -6984,13 +6984,13 @@
         </is>
       </c>
       <c r="H153" s="12" t="n">
-        <v>2376.0</v>
+        <v>1584.0</v>
       </c>
       <c r="I153" s="12" t="n">
-        <v>2232.0</v>
+        <v>1584.0</v>
       </c>
       <c r="J153" s="12" t="n">
-        <v>144.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="154">
@@ -7389,10 +7389,10 @@
         <v>350.0</v>
       </c>
       <c r="I162" s="12" t="n">
-        <v>89.0</v>
+        <v>105.0</v>
       </c>
       <c r="J162" s="12" t="n">
-        <v>261.0</v>
+        <v>245.0</v>
       </c>
     </row>
     <row r="163">
@@ -7478,10 +7478,10 @@
         </is>
       </c>
       <c r="H164" s="12" t="n">
-        <v>3168.0</v>
+        <v>0.0</v>
       </c>
       <c r="I164" s="12" t="n">
-        <v>3168.0</v>
+        <v>0.0</v>
       </c>
       <c r="J164" s="12" t="n">
         <v>0.0</v>
@@ -7527,10 +7527,10 @@
         <v>3456.0</v>
       </c>
       <c r="I165" s="12" t="n">
-        <v>3456.0</v>
+        <v>2592.0</v>
       </c>
       <c r="J165" s="12" t="n">
-        <v>0.0</v>
+        <v>864.0</v>
       </c>
     </row>
     <row r="166">
@@ -8729,10 +8729,10 @@
         <v>5616.0</v>
       </c>
       <c r="I192" s="12" t="n">
-        <v>0.0</v>
+        <v>936.0</v>
       </c>
       <c r="J192" s="12" t="n">
-        <v>5616.0</v>
+        <v>4680.0</v>
       </c>
     </row>
     <row r="193">
@@ -8944,10 +8944,10 @@
         </is>
       </c>
       <c r="H197" s="12" t="n">
-        <v>6912.0</v>
+        <v>4320.0</v>
       </c>
       <c r="I197" s="12" t="n">
-        <v>6912.0</v>
+        <v>4320.0</v>
       </c>
       <c r="J197" s="12" t="n">
         <v>0.0</v>
@@ -9073,10 +9073,10 @@
         <v>0.0</v>
       </c>
       <c r="I200" s="12" t="n">
-        <v>936.0</v>
+        <v>0.0</v>
       </c>
       <c r="J200" s="12" t="n">
-        <v>-936.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="201">
@@ -9456,10 +9456,10 @@
         </is>
       </c>
       <c r="H209" s="12" t="n">
-        <v>1872.0</v>
+        <v>0.0</v>
       </c>
       <c r="I209" s="12" t="n">
-        <v>1872.0</v>
+        <v>0.0</v>
       </c>
       <c r="J209" s="12" t="n">
         <v>0.0</v>
@@ -9505,10 +9505,10 @@
         <v>552.0</v>
       </c>
       <c r="I210" s="12" t="n">
-        <v>175.0</v>
+        <v>247.0</v>
       </c>
       <c r="J210" s="12" t="n">
-        <v>377.0</v>
+        <v>305.0</v>
       </c>
     </row>
     <row r="211">
@@ -11619,10 +11619,10 @@
         <v>224.0</v>
       </c>
       <c r="I257" s="12" t="n">
-        <v>89.0</v>
+        <v>109.0</v>
       </c>
       <c r="J257" s="12" t="n">
-        <v>135.0</v>
+        <v>115.0</v>
       </c>
     </row>
     <row r="258">
@@ -13189,10 +13189,10 @@
         <v>7128.0</v>
       </c>
       <c r="I292" s="12" t="n">
-        <v>6336.0</v>
+        <v>6768.0</v>
       </c>
       <c r="J292" s="12" t="n">
-        <v>792.0</v>
+        <v>360.0</v>
       </c>
     </row>
     <row r="293">
@@ -13917,10 +13917,10 @@
         <v>426.0</v>
       </c>
       <c r="I308" s="12" t="n">
-        <v>271.0</v>
+        <v>285.0</v>
       </c>
       <c r="J308" s="12" t="n">
-        <v>155.0</v>
+        <v>141.0</v>
       </c>
     </row>
     <row r="309">
@@ -14009,10 +14009,10 @@
         <v>300.0</v>
       </c>
       <c r="I310" s="12" t="n">
-        <v>247.0</v>
+        <v>261.0</v>
       </c>
       <c r="J310" s="12" t="n">
-        <v>53.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="311">
@@ -14055,10 +14055,10 @@
         <v>552.0</v>
       </c>
       <c r="I311" s="12" t="n">
-        <v>248.0</v>
+        <v>256.0</v>
       </c>
       <c r="J311" s="12" t="n">
-        <v>304.0</v>
+        <v>296.0</v>
       </c>
     </row>
     <row r="312">
@@ -15253,10 +15253,10 @@
         <v>2376.0</v>
       </c>
       <c r="I338" s="12" t="n">
-        <v>2196.0</v>
+        <v>2376.0</v>
       </c>
       <c r="J338" s="12" t="n">
-        <v>180.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="339">
@@ -16035,10 +16035,10 @@
         <v>3960.0</v>
       </c>
       <c r="I355" s="12" t="n">
-        <v>3600.0</v>
+        <v>3384.0</v>
       </c>
       <c r="J355" s="12" t="n">
-        <v>360.0</v>
+        <v>576.0</v>
       </c>
     </row>
     <row r="356">
@@ -16081,10 +16081,10 @@
         <v>1584.0</v>
       </c>
       <c r="I356" s="12" t="n">
-        <v>1008.0</v>
+        <v>1584.0</v>
       </c>
       <c r="J356" s="12" t="n">
-        <v>576.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="357">
@@ -19487,10 +19487,10 @@
         <v>1584.0</v>
       </c>
       <c r="I433" s="12" t="n">
-        <v>1152.0</v>
+        <v>1404.0</v>
       </c>
       <c r="J433" s="12" t="n">
-        <v>432.0</v>
+        <v>180.0</v>
       </c>
     </row>
     <row r="434">
